--- a/artfynd/A 33000-2025 artfynd.xlsx
+++ b/artfynd/A 33000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135616819</v>
       </c>
       <c r="B2" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135616835</v>
       </c>
       <c r="B3" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135616748</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>135616760</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33000-2025 artfynd.xlsx
+++ b/artfynd/A 33000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135616819</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135616835</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135616855</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>135616877</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135616880</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135616890</v>
       </c>
       <c r="B7" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135616748</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>135616760</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33000-2025 artfynd.xlsx
+++ b/artfynd/A 33000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135616819</v>
       </c>
       <c r="B2" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135616835</v>
       </c>
       <c r="B3" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135616748</v>
       </c>
       <c r="B8" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>135616760</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33000-2025 artfynd.xlsx
+++ b/artfynd/A 33000-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135616819</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135616835</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135616855</v>
       </c>
       <c r="B4" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>135616877</v>
       </c>
       <c r="B5" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135616880</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>135616890</v>
       </c>
       <c r="B7" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135616748</v>
       </c>
       <c r="B8" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>135616760</v>
       </c>
       <c r="B9" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
